--- a/Simulation/Results/p.mid_Censor.Ints_mean.surv.30.xlsx
+++ b/Simulation/Results/p.mid_Censor.Ints_mean.surv.30.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">mid</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3 mins</t>
+    <t xml:space="preserve">5.5 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4 mins</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0184</v>
+        <v>0.0137</v>
       </c>
       <c r="C2" t="n">
         <v>0.0001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0034</v>
+        <v>0.0022</v>
       </c>
       <c r="E2" t="n">
         <v>0.0333333333333333</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0175</v>
+        <v>0.0151</v>
       </c>
       <c r="C3" t="n">
         <v>0.0001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0011</v>
+        <v>0.0006</v>
       </c>
       <c r="E3" t="n">
         <v>0.0333333333333333</v>
@@ -506,7 +506,7 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0131</v>
+        <v>0.0122</v>
       </c>
       <c r="C5" t="n">
         <v>0.0001</v>
